--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,42 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -562,16 +598,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>67.86</v>
+      </c>
+      <c r="H2">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +624,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +701,7 @@
         <v>67.86</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,7 +727,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +767,98 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,42 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -507,19 +471,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,10 +497,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -545,7 +509,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -598,19 +562,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -624,10 +588,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -636,7 +600,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -689,19 +653,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -715,10 +679,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -727,7 +691,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -767,98 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920113</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920119</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20221.xlsx
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
